--- a/documents/42SH_PLAN.xlsx
+++ b/documents/42SH_PLAN.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="28109"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="28908"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/SD_CACHE/Dropbox_42/Dropbox/42_LOCAL/Documents/ANNEE_2/42SH/documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/SD_CACHE/dropbox_gmail/Dropbox/42_LOCAL/Documents/ANNEE_3/42SH/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1471,7 +1471,7 @@
   <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="56.1640625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="99.6640625" style="4" customWidth="1"/>
     <col min="2" max="2" width="19.6640625" style="4" customWidth="1"/>
     <col min="3" max="3" width="16.6640625" style="4" customWidth="1"/>
     <col min="4" max="4" width="17.83203125" style="4" customWidth="1"/>
@@ -1576,7 +1576,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>95</v>
       </c>
@@ -1586,7 +1586,7 @@
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
     </row>
-    <row r="9" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>96</v>
       </c>
@@ -1596,7 +1596,7 @@
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
     </row>
-    <row r="10" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>97</v>
       </c>
@@ -1606,7 +1606,7 @@
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
     </row>
-    <row r="11" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>98</v>
       </c>
@@ -1616,7 +1616,7 @@
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
     </row>
-    <row r="12" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>99</v>
       </c>
@@ -1626,7 +1626,7 @@
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
     </row>
-    <row r="13" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>100</v>
       </c>
@@ -1636,7 +1636,7 @@
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
     </row>
-    <row r="14" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>101</v>
       </c>
@@ -1646,7 +1646,7 @@
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
     </row>
-    <row r="15" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>102</v>
       </c>
@@ -1656,7 +1656,7 @@
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
     </row>
-    <row r="16" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>109</v>
       </c>
@@ -1666,7 +1666,7 @@
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
     </row>
-    <row r="17" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>103</v>
       </c>
@@ -1686,7 +1686,7 @@
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
     </row>
-    <row r="19" spans="1:4" ht="48" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>105</v>
       </c>
@@ -1735,7 +1735,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>88</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>89</v>
       </c>
@@ -1784,7 +1784,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>93</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>94</v>
       </c>
@@ -1808,7 +1808,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="64" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>81</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="48" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>82</v>
       </c>
@@ -1824,7 +1824,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>83</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="88" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>84</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="64" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>86</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>87</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="14" t="s">
         <v>73</v>
       </c>
@@ -1992,7 +1992,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>54</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="13" t="s">
         <v>55</v>
       </c>
@@ -2008,7 +2008,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
         <v>56</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
         <v>60</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="12" t="s">
         <v>62</v>
       </c>
